--- a/appium_tests/reports/app_e2e_report.xlsx
+++ b/appium_tests/reports/app_e2e_report.xlsx
@@ -72,7 +72,7 @@
     <t>Total Duration</t>
   </si>
   <si>
-    <t>378.71 seconds</t>
+    <t>377.95 seconds</t>
   </si>
   <si>
     <t>Default Timeout</t>
@@ -84,7 +84,7 @@
     <t>Report Generated On</t>
   </si>
   <si>
-    <t>13/6/2026, 10:21:25 am</t>
+    <t>18/6/2026, 1:06:21 pm</t>
   </si>
   <si>
     <t>Test Runner</t>
@@ -120,7 +120,7 @@
     <t>Mother</t>
   </si>
   <si>
-    <t>04:45:06</t>
+    <t>07:30:03</t>
   </si>
   <si>
     <t>Launching Life Nest app and waiting for splash (4500ms)</t>
@@ -132,13 +132,13 @@
     <t/>
   </si>
   <si>
-    <t>04:45:11</t>
+    <t>07:30:09</t>
   </si>
   <si>
     <t>Tap "Create new account"</t>
   </si>
   <si>
-    <t>04:45:12</t>
+    <t>07:30:10</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Please select your role to continue"</t>
@@ -147,76 +147,76 @@
     <t>Select "Mother" role card</t>
   </si>
   <si>
-    <t>04:45:13</t>
+    <t>07:30:11</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Welcome, Mother!"</t>
   </si>
   <si>
-    <t>04:45:22</t>
-  </si>
-  <si>
-    <t>Enter Full Name: Jane Doe 51468</t>
-  </si>
-  <si>
-    <t>04:45:32</t>
+    <t>07:30:20</t>
+  </si>
+  <si>
+    <t>Enter Full Name: Jane Doe 37434</t>
+  </si>
+  <si>
+    <t>07:30:29</t>
   </si>
   <si>
     <t>Enter Phone Number: 9876543210</t>
   </si>
   <si>
-    <t>04:45:41</t>
+    <t>07:30:39</t>
   </si>
   <si>
     <t>Enter Password: *******</t>
   </si>
   <si>
-    <t>04:45:42</t>
+    <t>07:30:40</t>
   </si>
   <si>
     <t>Pressed keyboard Done key to submit registration form</t>
   </si>
   <si>
-    <t>04:45:43</t>
+    <t>07:30:41</t>
   </si>
   <si>
     <t>adb reverse tunnel re-applied (phone → PC backend:8000)</t>
   </si>
   <si>
-    <t>04:45:51</t>
+    <t>07:30:49</t>
   </si>
   <si>
     <t xml:space="preserve">Screen after Create Account (8s): </t>
   </si>
   <si>
-    <t>04:45:52</t>
-  </si>
-  <si>
     <t>Verified screen element containing text/label: "Let's build your profile, Mom!"</t>
   </si>
   <si>
-    <t>04:45:53</t>
+    <t>07:30:50</t>
   </si>
   <si>
     <t>Input Age: 27</t>
   </si>
   <si>
-    <t>04:46:00</t>
+    <t>07:30:58</t>
   </si>
   <si>
     <t>Input Weight: 62 kg</t>
   </si>
   <si>
-    <t>04:46:02</t>
+    <t>07:30:59</t>
   </si>
   <si>
     <t>Opening dropdown for "Blood Group"</t>
   </si>
   <si>
+    <t>07:31:00</t>
+  </si>
+  <si>
     <t>Tapped "Blood Group"</t>
   </si>
   <si>
-    <t>04:46:22</t>
+    <t>07:31:20</t>
   </si>
   <si>
     <t>Blood Group dropdown skipped, default O+ retained: Could not find tappable element for "AB+".</t>
@@ -225,55 +225,55 @@
     <t>Warning</t>
   </si>
   <si>
-    <t>04:46:23</t>
+    <t>07:31:21</t>
   </si>
   <si>
     <t>Input Weeks Pregnant: 14</t>
   </si>
   <si>
-    <t>04:46:26</t>
+    <t>07:31:23</t>
   </si>
   <si>
     <t>Open due date picker</t>
   </si>
   <si>
-    <t>04:46:28</t>
+    <t>07:31:26</t>
   </si>
   <si>
     <t>Confirm pre-selected due date</t>
   </si>
   <si>
-    <t>04:46:33</t>
+    <t>07:31:33</t>
   </si>
   <si>
     <t>Input Phone Number: 9876543210</t>
   </si>
   <si>
-    <t>04:46:35</t>
+    <t>07:31:35</t>
   </si>
   <si>
     <t>Input Address</t>
   </si>
   <si>
-    <t>04:46:43</t>
+    <t>07:31:43</t>
   </si>
   <si>
     <t>Input Emergency Contact</t>
   </si>
   <si>
-    <t>04:46:46</t>
+    <t>07:31:46</t>
   </si>
   <si>
     <t>Select "Dairy" allergy chip</t>
   </si>
   <si>
-    <t>04:46:50</t>
+    <t>07:31:49</t>
   </si>
   <si>
     <t>Tap "Complete Setup" to save Mother profile</t>
   </si>
   <si>
-    <t>04:47:40</t>
+    <t>07:32:40</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Tools"</t>
@@ -282,13 +282,13 @@
     <t>Successfully reached Mother Dashboard</t>
   </si>
   <si>
-    <t>04:47:58</t>
+    <t>07:32:58</t>
   </si>
   <si>
     <t>Hydration Tracker feature skipped: Could not find tappable element for "Hydration Tracker".</t>
   </si>
   <si>
-    <t>04:48:16</t>
+    <t>07:33:16</t>
   </si>
   <si>
     <t>Kick Counter feature skipped: Could not find tappable element for "Kick Counter".</t>
@@ -303,82 +303,82 @@
     <t>Doctor</t>
   </si>
   <si>
-    <t>04:48:17</t>
+    <t>07:33:17</t>
   </si>
   <si>
     <t>App data cleared for clean launch</t>
   </si>
   <si>
-    <t>04:48:18</t>
-  </si>
-  <si>
-    <t>04:48:24</t>
-  </si>
-  <si>
-    <t>04:48:25</t>
-  </si>
-  <si>
-    <t>04:48:26</t>
+    <t>07:33:18</t>
+  </si>
+  <si>
+    <t>07:33:24</t>
+  </si>
+  <si>
+    <t>07:33:25</t>
+  </si>
+  <si>
+    <t>07:33:26</t>
   </si>
   <si>
     <t>Select "Doctor" role</t>
   </si>
   <si>
-    <t>04:48:27</t>
+    <t>07:33:27</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Welcome, Doctor!"</t>
   </si>
   <si>
-    <t>04:48:36</t>
-  </si>
-  <si>
-    <t>Enter Full Name: Dr. House 79981</t>
-  </si>
-  <si>
-    <t>04:48:45</t>
+    <t>07:33:36</t>
+  </si>
+  <si>
+    <t>Enter Full Name: Dr. House 12652</t>
+  </si>
+  <si>
+    <t>07:33:45</t>
   </si>
   <si>
     <t>Enter Phone Number: 8888888888</t>
   </si>
   <si>
-    <t>04:48:54</t>
-  </si>
-  <si>
-    <t>04:48:55</t>
-  </si>
-  <si>
-    <t>04:49:03</t>
-  </si>
-  <si>
-    <t>04:49:48</t>
+    <t>07:33:54</t>
+  </si>
+  <si>
+    <t>07:33:55</t>
+  </si>
+  <si>
+    <t>07:34:03</t>
+  </si>
+  <si>
+    <t>07:34:49</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Mothers"</t>
   </si>
   <si>
-    <t>Verified Doctor dashboard access for: Dr. House 79981</t>
-  </si>
-  <si>
-    <t>04:50:00</t>
+    <t>Verified Doctor dashboard access for: Dr. House 12652</t>
+  </si>
+  <si>
+    <t>07:35:00</t>
   </si>
   <si>
     <t>Open Mothers tab</t>
   </si>
   <si>
-    <t>04:50:12</t>
+    <t>07:35:13</t>
   </si>
   <si>
     <t>Open Today tab</t>
   </si>
   <si>
-    <t>04:50:25</t>
+    <t>07:35:25</t>
   </si>
   <si>
     <t>Return to Overview tab</t>
   </si>
   <si>
-    <t>04:50:26</t>
+    <t>07:35:26</t>
   </si>
   <si>
     <t>Health Worker Role - Registration and Dashboard Verification</t>
@@ -387,55 +387,55 @@
     <t>Health Worker</t>
   </si>
   <si>
-    <t>04:50:27</t>
-  </si>
-  <si>
-    <t>04:50:33</t>
-  </si>
-  <si>
-    <t>04:50:35</t>
+    <t>07:35:27</t>
+  </si>
+  <si>
+    <t>07:35:33</t>
+  </si>
+  <si>
+    <t>07:35:35</t>
   </si>
   <si>
     <t>Select "Health Worker" role</t>
   </si>
   <si>
-    <t>04:50:36</t>
+    <t>07:35:36</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Welcome, Health Worker!"</t>
   </si>
   <si>
-    <t>04:50:45</t>
-  </si>
-  <si>
-    <t>Enter Full Name: Nurse Brenda 51132</t>
-  </si>
-  <si>
-    <t>04:50:54</t>
+    <t>07:35:45</t>
+  </si>
+  <si>
+    <t>Enter Full Name: Nurse Brenda 38873</t>
+  </si>
+  <si>
+    <t>07:35:54</t>
   </si>
   <si>
     <t>Enter Phone Number: 7777777777</t>
   </si>
   <si>
-    <t>04:51:03</t>
-  </si>
-  <si>
-    <t>04:51:04</t>
-  </si>
-  <si>
-    <t>04:51:12</t>
+    <t>07:36:04</t>
+  </si>
+  <si>
+    <t>07:36:05</t>
+  </si>
+  <si>
+    <t>07:36:13</t>
   </si>
   <si>
     <t>Verified screen element containing text/label: "Assign mother"</t>
   </si>
   <si>
-    <t>Verified Health Worker Dashboard access for: Nurse Brenda 51132</t>
-  </si>
-  <si>
-    <t>04:51:25</t>
-  </si>
-  <si>
-    <t>Worker name banner not found</t>
+    <t>Verified Health Worker Dashboard access for: Nurse Brenda 38873</t>
+  </si>
+  <si>
+    <t>07:36:21</t>
+  </si>
+  <si>
+    <t>Verified worker name is shown on the dashboard banner</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -459,7 +459,7 @@
     <t>Mother App E2E</t>
   </si>
   <si>
-    <t>Launching Life Nest app and waiting for splash (4500ms) | Tap "Create new account" | Verified screen element containing text/label: "Please select your role to continue" | Select "Mother" role card | Verified screen element containing text/label: "Welcome, Mother!" | Enter Full Name: Jane Doe 51468 | Enter Phone Number: 9876543210 | Enter Password: ******* | Pressed keyboard Done key to submit registration form | adb reverse tunnel re-applied (phone → PC backend:8000) | Screen after Create Account (8s):  | Verified screen element containing text/label: "Let's build your profile, Mom!" | Input Age: 27 | Input Weight: 62 kg | Opening dropdown for "Blood Group" | Tapped "Blood Group" | Blood Group dropdown skipped, default O+ retained: Could not find tappable element for "AB+". | Input Weeks Pregnant: 14 | Open due date picker | Confirm pre-selected due date | Input Phone Number: 9876543210 | Input Address | Input Emergency Contact | Select "Dairy" allergy chip | Tap "Complete Setup" to save Mother profile | Verified screen element containing text/label: "Tools" | Successfully reached Mother Dashboard | Hydration Tracker feature skipped: Could not find tappable element for "Hydration Tracker". | Kick Counter feature skipped: Could not find tappable element for "Kick Counter". | Test completed successfully.</t>
+    <t>Launching Life Nest app and waiting for splash (4500ms) | Tap "Create new account" | Verified screen element containing text/label: "Please select your role to continue" | Select "Mother" role card | Verified screen element containing text/label: "Welcome, Mother!" | Enter Full Name: Jane Doe 37434 | Enter Phone Number: 9876543210 | Enter Password: ******* | Pressed keyboard Done key to submit registration form | adb reverse tunnel re-applied (phone → PC backend:8000) | Screen after Create Account (8s):  | Verified screen element containing text/label: "Let's build your profile, Mom!" | Input Age: 27 | Input Weight: 62 kg | Opening dropdown for "Blood Group" | Tapped "Blood Group" | Blood Group dropdown skipped, default O+ retained: Could not find tappable element for "AB+". | Input Weeks Pregnant: 14 | Open due date picker | Confirm pre-selected due date | Input Phone Number: 9876543210 | Input Address | Input Emergency Contact | Select "Dairy" allergy chip | Tap "Complete Setup" to save Mother profile | Verified screen element containing text/label: "Tools" | Successfully reached Mother Dashboard | Hydration Tracker feature skipped: Could not find tappable element for "Hydration Tracker". | Kick Counter feature skipped: Could not find tappable element for "Kick Counter". | Test completed successfully.</t>
   </si>
   <si>
     <t>Pass</t>
@@ -471,7 +471,7 @@
     <t>Doctor App E2E</t>
   </si>
   <si>
-    <t>App data cleared for clean launch | Launching Life Nest app and waiting for splash (4500ms) | Tap "Create new account" | Verified screen element containing text/label: "Please select your role to continue" | Select "Doctor" role | Verified screen element containing text/label: "Welcome, Doctor!" | Enter Full Name: Dr. House 79981 | Enter Phone Number: 8888888888 | Enter Password: ******* | Pressed keyboard Done key to submit registration form | adb reverse tunnel re-applied (phone → PC backend:8000) | Screen after Create Account (8s):  | Verified screen element containing text/label: "Mothers" | Verified Doctor dashboard access for: Dr. House 79981 | Open Mothers tab | Open Today tab | Return to Overview tab | Test completed successfully.</t>
+    <t>App data cleared for clean launch | Launching Life Nest app and waiting for splash (4500ms) | Tap "Create new account" | Verified screen element containing text/label: "Please select your role to continue" | Select "Doctor" role | Verified screen element containing text/label: "Welcome, Doctor!" | Enter Full Name: Dr. House 12652 | Enter Phone Number: 8888888888 | Enter Password: ******* | Pressed keyboard Done key to submit registration form | adb reverse tunnel re-applied (phone → PC backend:8000) | Screen after Create Account (8s):  | Verified screen element containing text/label: "Mothers" | Verified Doctor dashboard access for: Dr. House 12652 | Open Mothers tab | Open Today tab | Return to Overview tab | Test completed successfully.</t>
   </si>
   <si>
     <t>APP-E2E-003</t>
@@ -480,7 +480,7 @@
     <t>Health Worker App E2E</t>
   </si>
   <si>
-    <t>App data cleared for clean launch | Launching Life Nest app and waiting for splash (4500ms) | Tap "Create new account" | Verified screen element containing text/label: "Please select your role to continue" | Select "Health Worker" role | Verified screen element containing text/label: "Welcome, Health Worker!" | Enter Full Name: Nurse Brenda 51132 | Enter Phone Number: 7777777777 | Enter Password: ******* | Pressed keyboard Done key to submit registration form | adb reverse tunnel re-applied (phone → PC backend:8000) | Screen after Create Account (8s):  | Verified screen element containing text/label: "Assign mother" | Verified Health Worker Dashboard access for: Nurse Brenda 51132 | Worker name banner not found | Test completed successfully.</t>
+    <t>App data cleared for clean launch | Launching Life Nest app and waiting for splash (4500ms) | Tap "Create new account" | Verified screen element containing text/label: "Please select your role to continue" | Select "Health Worker" role | Verified screen element containing text/label: "Welcome, Health Worker!" | Enter Full Name: Nurse Brenda 38873 | Enter Phone Number: 7777777777 | Enter Password: ******* | Pressed keyboard Done key to submit registration form | adb reverse tunnel re-applied (phone → PC backend:8000) | Screen after Create Account (8s):  | Verified screen element containing text/label: "Assign mother" | Verified Health Worker Dashboard access for: Nurse Brenda 38873 | Verified worker name is shown on the dashboard banner | Test completed successfully.</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1186,7 @@
         <v>37</v>
       </c>
       <c r="G2" s="4">
-        <v>190.33</v>
+        <v>193.69</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1430,10 +1430,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>37</v>
@@ -1453,10 +1453,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>37</v>
@@ -1476,10 +1476,10 @@
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>37</v>
@@ -1499,10 +1499,10 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>37</v>
@@ -1522,7 +1522,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>66</v>
@@ -1876,7 +1876,7 @@
         <v>37</v>
       </c>
       <c r="G33" s="6">
-        <v>129.7</v>
+        <v>129.78</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2290,7 +2290,7 @@
         <v>37</v>
       </c>
       <c r="G52" s="4">
-        <v>58.68</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2608,8 +2608,8 @@
       <c r="E66" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F66" s="12" t="s">
-        <v>69</v>
+      <c r="F66" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>38</v>
